--- a/practice/answers/q102.xlsx
+++ b/practice/answers/q102.xlsx
@@ -7,13 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PivotTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId3"/>
+    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,11 +47,22 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0024302A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +74,18 @@
         <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,11 +93,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A9C4AE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A9C4AE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A9C4AE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A9C4AE"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,7 +132,24 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22362,6 +22423,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004A7C59"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Question 37 — Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Variety on Rows, Year on Columns and Acres shown as Sum; use the visible Grand Total column for overall totals.</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>AAC Brandon is first (about 6.74 million acres), AAC Starbuck second (2.50 million) and AAC Wheatland third (1.40 million). AAC Brandon declines every year, from about 1.64 million acres in 2020 to 0.79 million in 2025.</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Acres are additive quantities. Yield is a per-acre rate, so adding yields would not give a meaningful total.</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>The live PivotTable (and chart, where requested) is on the PivotTable worksheet. The highlighted rows there show the values used in the written answers. The Data worksheet contains the source records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A9:D10"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -96757,13 +96918,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -96776,907 +96937,918 @@
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Q102 — Variety × Year</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2"/>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Sum of Acres</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Sum of Acres</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
+          <t>Variety</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Variety</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AAC ALIDA (BW980)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>7192</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1231</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n">
+        <v>8423</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AAC ALIDA (BW980)</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>7192</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>1231</v>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="7" t="n">
-        <v>8423</v>
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>AAC BRANDON (BW 932)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>1644428.2</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>1257061.6</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>1123634.2</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>1024022.2</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>904854.7999999999</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>787111.3999999999</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>6741112.399999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AAC BRANDON (BW 932)</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>1644428.2</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>1257061.6</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1123634.2</v>
-      </c>
+          <t>AAC BROADACRES &lt;PROVEN&gt;</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n">
-        <v>1024022.2</v>
+        <v>1340</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>904854.7999999999</v>
+        <v>8351</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>787111.3999999999</v>
+        <v>18034</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>6741112.399999999</v>
+        <v>27725</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AAC BROADACRES &lt;PROVEN&gt;</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n">
-        <v>1340</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>8351</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>18034</v>
-      </c>
+          <t>AAC CAMERON VB &lt;CANTERRA&gt;</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>15834</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>14011</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1039</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>27725</v>
+        <v>30884</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AAC CAMERON VB &lt;CANTERRA&gt;</t>
+          <t>AAC CONNERY |PT245|</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>15834</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>14011</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>1039</v>
-      </c>
+        <v>3224</v>
+      </c>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="7" t="n">
-        <v>30884</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AAC CONNERY |PT245|</t>
+          <t>AAC ELIE(BW931)</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3224</v>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+        <v>132819.5</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>73537</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>44806.5</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>39714</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>34606</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>31067</v>
+      </c>
       <c r="H10" s="7" t="n">
-        <v>3224</v>
+        <v>356550</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AAC ELIE(BW931)</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>132819.5</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>73537</v>
-      </c>
+          <t>AAC HOCKLEY |BW5044|</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n">
-        <v>44806.5</v>
+        <v>2577</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>39714</v>
+        <v>137008.8</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>34606</v>
+        <v>198035.1</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>31067</v>
+        <v>250422.9</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>356550</v>
+        <v>588043.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AAC HOCKLEY |BW5044|</t>
+          <t>AAC HODGE |BW1069|</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n">
-        <v>2577</v>
-      </c>
+      <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n">
-        <v>137008.8</v>
+        <v>63370</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>198035.1</v>
+        <v>91081.5</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>250422.9</v>
+        <v>22247</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>588043.8</v>
+        <v>176698.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AAC HODGE |BW1069|</t>
+          <t>AAC LEROY VB &lt;ALLIANCE&gt;</t>
         </is>
       </c>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>17545</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>32463</v>
+      </c>
       <c r="E13" s="6" t="n">
-        <v>63370</v>
+        <v>35456</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>91081.5</v>
+        <v>23689</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>22247</v>
+        <v>17908</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>176698.5</v>
+        <v>127061</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AAC LEROY VB &lt;ALLIANCE&gt;</t>
+          <t>AAC MAGNET |BW 1045, BJ14*A01135|</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>17545</v>
+        <v>892</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>32463</v>
+        <v>680</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>35456</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>23689</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>17908</v>
-      </c>
+        <v>1348</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="7" t="n">
-        <v>127061</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AAC MAGNET |BW 1045, BJ14*A01135|</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
+          <t>AAC REDBERRY</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>124319</v>
+      </c>
       <c r="C15" s="6" t="n">
-        <v>892</v>
+        <v>110048.1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>680</v>
+        <v>91246.2</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1348</v>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+        <v>70657</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>51063.1</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>27095.7</v>
+      </c>
       <c r="H15" s="7" t="n">
-        <v>2920</v>
+        <v>474429.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AAC REDBERRY</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>124319</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>110048.1</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>91246.2</v>
-      </c>
+          <t>AAC REDSTAR &lt;SECAN&gt; |PT488|</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n">
-        <v>70657</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>51063.1</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>27095.7</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="7" t="n">
-        <v>474429.1</v>
+        <v>532</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AAC REDSTAR &lt;SECAN&gt; |PT488|</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
+          <t>AAC REDWATER (PT457)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1034</v>
+      </c>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n">
-        <v>532</v>
-      </c>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="7" t="n">
-        <v>532</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAC REDWATER (PT457)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>1034</v>
-      </c>
+          <t>AAC SPIKE</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>1361</v>
+      </c>
       <c r="H18" s="7" t="n">
-        <v>1034</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>AAC SPIKE</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n">
-        <v>1361</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>1361</v>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>AAC STARBUCK &lt;SECAN&gt;</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n">
+        <v>4929</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>286941.4</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>505262.5</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>599098.4</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>550969.7</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <v>556737.7</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>2503938.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AAC STARBUCK &lt;SECAN&gt;</t>
+          <t>AAC TISDALE (PT250)</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>4929</v>
+        <v>26898</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>286941.4</v>
+        <v>17277</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>505262.5</v>
+        <v>5941</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>599098.4</v>
+        <v>3502</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>550969.7</v>
+        <v>1162</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>556737.7</v>
+        <v>579</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>2503938.7</v>
+        <v>55359</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AAC TISDALE (PT250)</t>
+          <t>AAC VIEWFIELD &lt;FP GENETICS&gt;|BW965| EXP</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>26898</v>
+        <v>292344</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>17277</v>
+        <v>180211</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>5941</v>
+        <v>179139</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>3502</v>
+        <v>174234</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1162</v>
+        <v>147597</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>579</v>
+        <v>140771.5</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>55359</v>
+        <v>1114296.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AAC VIEWFIELD &lt;FP GENETICS&gt;|BW965| EXP</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>292344</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>180211</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>179139</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>174234</v>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>147597</v>
-      </c>
+          <t>AAC WESTKING</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n">
-        <v>140771.5</v>
+        <v>16727</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1114296.5</v>
+        <v>16727</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AAC WESTKING</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n">
-        <v>16727</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>16727</v>
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>AAC WHEATLAND &lt;SECAN&gt;</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>1964</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>120199.8</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>220164.5</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>312660.5</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>343688.7</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <v>400415.7</v>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>1399093.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AAC WHEATLAND &lt;SECAN&gt;</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>1964</v>
-      </c>
+          <t>AC BARRIE (BW 661)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n">
-        <v>120199.8</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>220164.5</v>
-      </c>
+        <v>1380</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n">
-        <v>312660.5</v>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>343688.7</v>
-      </c>
+        <v>917</v>
+      </c>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n">
-        <v>400415.7</v>
+        <v>527</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1399093.2</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AC BARRIE (BW 661)</t>
+          <t>AC CADILLAC (BW 689)</t>
         </is>
       </c>
       <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n">
-        <v>1380</v>
-      </c>
+      <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n">
-        <v>917</v>
-      </c>
+      <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n">
-        <v>527</v>
+        <v>653</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>2824</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AC CADILLAC (BW 689)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
+          <t>AC DOMAIN (BW 148)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>2897</v>
+      </c>
       <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
+      <c r="D26" s="6" t="n">
+        <v>1321</v>
+      </c>
       <c r="E26" s="6" t="n"/>
       <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n">
-        <v>653</v>
-      </c>
+      <c r="G26" s="6" t="n"/>
       <c r="H26" s="7" t="n">
-        <v>653</v>
+        <v>4218</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AC DOMAIN (BW 148)</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>2897</v>
-      </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n">
-        <v>1321</v>
-      </c>
+          <t>AC SPLENDOR (BW 191)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>592</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="6" t="n"/>
       <c r="H27" s="7" t="n">
-        <v>4218</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AC SPLENDOR (BW 191)</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n">
-        <v>592</v>
-      </c>
+          <t>AC STETTLER &lt;SECAN&gt; |BW867|</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>962</v>
+      </c>
+      <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
       <c r="F28" s="6" t="n"/>
       <c r="G28" s="6" t="n"/>
       <c r="H28" s="7" t="n">
-        <v>592</v>
+        <v>962</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AC STETTLER &lt;SECAN&gt; |BW867|</t>
+          <t>BOLLES &lt;SEED DEPOT&gt;</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>962</v>
-      </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
+        <v>49734</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>89746</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>46776</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>39239</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>21640</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>26459</v>
+      </c>
       <c r="H29" s="7" t="n">
-        <v>962</v>
+        <v>273594</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BOLLES &lt;SEED DEPOT&gt;</t>
+          <t>CARBERRY (BW874)</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>49734</v>
-      </c>
-      <c r="C30" s="6" t="n">
-        <v>89746</v>
-      </c>
+        <v>5828</v>
+      </c>
+      <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n">
-        <v>46776</v>
+        <v>1430</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>39239</v>
-      </c>
-      <c r="F30" s="6" t="n">
-        <v>21640</v>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>26459</v>
-      </c>
+        <v>3257</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
       <c r="H30" s="7" t="n">
-        <v>273594</v>
+        <v>10515</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CARBERRY (BW874)</t>
+          <t>CARDALE (BW429)</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>5828</v>
-      </c>
-      <c r="C31" s="6" t="n"/>
+        <v>54059</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>23648</v>
+      </c>
       <c r="D31" s="6" t="n">
-        <v>1430</v>
+        <v>14014.1</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>3257</v>
-      </c>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
+        <v>10270</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>2757</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>5992</v>
+      </c>
       <c r="H31" s="7" t="n">
-        <v>10515</v>
+        <v>110740.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CARDALE (BW429)</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>54059</v>
-      </c>
-      <c r="C32" s="6" t="n">
-        <v>23648</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>14014.1</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>10270</v>
-      </c>
-      <c r="F32" s="6" t="n">
-        <v>2757</v>
-      </c>
+          <t>CDC ENVY</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
       <c r="G32" s="6" t="n">
-        <v>5992</v>
+        <v>2050</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>110740.1</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CDC ENVY</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
+          <t>CDC GO (BW781)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>2074</v>
+      </c>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
       <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n">
-        <v>2050</v>
-      </c>
+      <c r="G33" s="6" t="n"/>
       <c r="H33" s="7" t="n">
-        <v>2050</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CDC GO (BW781)</t>
+          <t>CDC HUGHES &lt;CPSC&gt; |PT588|</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>2074</v>
+        <v>3461</v>
       </c>
       <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
+      <c r="D34" s="6" t="n">
+        <v>698</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>909</v>
+      </c>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="7" t="n">
-        <v>2074</v>
+        <v>5068</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CDC HUGHES &lt;CPSC&gt; |PT588|</t>
+          <t>CDC IMAGINE (BW758)(IMI)</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3461</v>
+        <v>2171</v>
       </c>
       <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n">
-        <v>698</v>
-      </c>
-      <c r="E35" s="6" t="n">
-        <v>909</v>
-      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="7" t="n">
-        <v>5068</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CDC IMAGINE (BW758)(IMI)</t>
+          <t>CDC LANDMARK</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>2171</v>
-      </c>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
+        <v>38525</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>20781</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>14869</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>10095</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>5486</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>2200</v>
+      </c>
       <c r="H36" s="7" t="n">
-        <v>2171</v>
+        <v>91956</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CDC LANDMARK</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="n">
-        <v>38525</v>
-      </c>
+          <t>CDC ORTONA &lt;PROVEN&gt;</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n">
-        <v>20781</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <v>14869</v>
-      </c>
-      <c r="E37" s="6" t="n">
-        <v>10095</v>
-      </c>
-      <c r="F37" s="6" t="n">
-        <v>5486</v>
-      </c>
+        <v>819</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
       <c r="G37" s="6" t="n">
-        <v>2200</v>
+        <v>588</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>91956</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CDC ORTONA &lt;PROVEN&gt;</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n"/>
+          <t>CDC PLENTIFUL (PT580)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>15423</v>
+      </c>
       <c r="C38" s="6" t="n">
-        <v>819</v>
-      </c>
-      <c r="D38" s="6" t="n"/>
+        <v>2952</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>2587</v>
+      </c>
       <c r="E38" s="6" t="n"/>
       <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n">
-        <v>588</v>
-      </c>
+      <c r="G38" s="6" t="n"/>
       <c r="H38" s="7" t="n">
-        <v>1407</v>
+        <v>20962</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CDC PLENTIFUL (PT580)</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>15423</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>2952</v>
-      </c>
-      <c r="D39" s="6" t="n">
-        <v>2587</v>
-      </c>
-      <c r="E39" s="6" t="n"/>
+          <t>CDC SKRUSH |PT599|</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+      <c r="E39" s="6" t="n">
+        <v>1224</v>
+      </c>
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="6" t="n"/>
       <c r="H39" s="7" t="n">
-        <v>20962</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CDC SKRUSH |PT599|</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n">
-        <v>1224</v>
-      </c>
+          <t>CDC STANLEY (BW880)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>6970</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>3789</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>2262</v>
+      </c>
+      <c r="E40" s="6" t="n"/>
       <c r="F40" s="6" t="n"/>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="7" t="n">
-        <v>1224</v>
+        <v>13021</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CDC STANLEY (BW880)</t>
+          <t>CS DAYBREAK &lt;CANTERRA&gt;</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
-        <v>6970</v>
+        <v>3361</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>3789</v>
+        <v>5552</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2262</v>
-      </c>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
+        <v>8054</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>13279</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>2238</v>
+      </c>
       <c r="G41" s="6" t="n"/>
       <c r="H41" s="7" t="n">
-        <v>13021</v>
+        <v>32484</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CS DAYBREAK &lt;CANTERRA&gt;</t>
+          <t>GLENN</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
-        <v>3361</v>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>5552</v>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>8054</v>
-      </c>
-      <c r="E42" s="6" t="n">
-        <v>13279</v>
-      </c>
-      <c r="F42" s="6" t="n">
-        <v>2238</v>
-      </c>
+        <v>4793</v>
+      </c>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n"/>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n"/>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="7" t="n">
-        <v>32484</v>
+        <v>4793</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GLENN</t>
+          <t>HARVEST (BW259)</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
-        <v>4793</v>
+        <v>1045</v>
       </c>
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n"/>
@@ -97684,172 +97856,154 @@
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="6" t="n"/>
       <c r="H43" s="7" t="n">
-        <v>4793</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HARVEST (BW259)</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="n">
-        <v>1045</v>
-      </c>
+          <t>SHELLY</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
       <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
+      <c r="D44" s="6" t="n">
+        <v>657</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>720</v>
+      </c>
       <c r="F44" s="6" t="n"/>
       <c r="G44" s="6" t="n"/>
       <c r="H44" s="7" t="n">
-        <v>1045</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHELLY</t>
+          <t>SY CAST</t>
         </is>
       </c>
       <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
+      <c r="C45" s="6" t="n">
+        <v>520</v>
+      </c>
       <c r="D45" s="6" t="n">
-        <v>657</v>
+        <v>3396</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>720</v>
-      </c>
-      <c r="F45" s="6" t="n"/>
+        <v>3365</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>2011</v>
+      </c>
       <c r="G45" s="6" t="n"/>
       <c r="H45" s="7" t="n">
-        <v>1377</v>
+        <v>9292</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SY CAST</t>
+          <t>SY GABBRO &lt;SYNGENTA&gt;</t>
         </is>
       </c>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n">
-        <v>520</v>
+        <v>8280</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>3396</v>
+        <v>8492</v>
       </c>
       <c r="E46" s="6" t="n">
-        <v>3365</v>
+        <v>4107</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>2011</v>
-      </c>
-      <c r="G46" s="6" t="n"/>
+        <v>2227</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>1120</v>
+      </c>
       <c r="H46" s="7" t="n">
-        <v>9292</v>
+        <v>24226</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SY GABBRO &lt;SYNGENTA&gt;</t>
+          <t>SY MANNESS</t>
         </is>
       </c>
       <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n">
-        <v>8280</v>
-      </c>
-      <c r="D47" s="6" t="n">
-        <v>8492</v>
-      </c>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
       <c r="E47" s="6" t="n">
-        <v>4107</v>
+        <v>19186</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>2227</v>
+        <v>110145</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>1120</v>
+        <v>259696</v>
       </c>
       <c r="H47" s="7" t="n">
-        <v>24226</v>
+        <v>389027</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SY MANNESS</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
+          <t>SY TORACH &lt;SYNGENTA&gt;</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>7860</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>10153</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>6981</v>
+      </c>
       <c r="E48" s="6" t="n">
-        <v>19186</v>
+        <v>5488</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>110145</v>
+        <v>2120</v>
       </c>
       <c r="G48" s="6" t="n">
-        <v>259696</v>
+        <v>1914.8</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>389027</v>
+        <v>34516.8</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SY TORACH &lt;SYNGENTA&gt;</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>7860</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>10153</v>
-      </c>
-      <c r="D49" s="6" t="n">
-        <v>6981</v>
-      </c>
-      <c r="E49" s="6" t="n">
-        <v>5488</v>
-      </c>
-      <c r="F49" s="6" t="n">
-        <v>2120</v>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>1914.8</v>
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Grand Total</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>2454148.7</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>2247166.9</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>2318490</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>2574998.9</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>2503721.9</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>2571677.7</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>34516.8</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>2454148.7</v>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>2247166.9</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>2318490</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>2574998.9</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>2503721.9</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>2571677.7</v>
-      </c>
-      <c r="H50" s="7" t="n">
         <v>14670204.1</v>
       </c>
     </row>
